--- a/louis/docs/부서별 AI프로그램 개발 필요사항 취합자료.xlsx
+++ b/louis/docs/부서별 AI프로그램 개발 필요사항 취합자료.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\toyota_project\MCB-ML-toyota_project\louis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\toyota_project\toyota_project\louis\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E755070-843A-4CFF-9D89-C345F677A4E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70647FA7-1615-4DF7-9665-3F146EFCAF8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38580" yWindow="3705" windowWidth="13830" windowHeight="7110" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HND_Sales" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="210">
   <si>
     <t>AI프로그램 개발 관련 부서별 요청사항</t>
   </si>
@@ -264,9 +264,6 @@
     <t>연말이면 기존 데이터가 쌓여있어야하므로 최소 3년 데이터 필요</t>
   </si>
   <si>
-    <t>- 딜러사별 연말 KPI 결과 예측</t>
-  </si>
-  <si>
     <t>- 현재는 1) 딜러별/월별 화면 2) 딜러사별 비교화면 두개로 되어 있고, 이를 개별 다운로드후 작업</t>
   </si>
   <si>
@@ -310,9 +307,6 @@
   </si>
   <si>
     <t xml:space="preserve">  &gt;&gt; 연결하여 붙여넣기 실행 시 엑셀 구동이 안됨 (메모리 문제)</t>
-  </si>
-  <si>
-    <t>딜러별 A3 사이즈로 총 16개의 엑셀시트로 구성해서 이후 pdf로 변환 후 CEO 전달</t>
   </si>
   <si>
     <t>- Overall HSIT Monthly KPI by DLR (DMS-KPI) 월별/분기별/연도별 데이터</t>
@@ -657,6 +651,42 @@
   </si>
   <si>
     <t>-향후 계약 IP 동향 분석</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>원가/원가+수수료</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>수수료만 빼서 보면되긴하는데</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>요인: 금리/카드 사용횟수, 결제 금액 규모 등</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 딜러사별 연말 KPI 결과 예측</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>딜러별 A3 사이즈로 총 16개의 엑셀시트로 구성해서 이후 pdf로 변환 후 CEO 전달</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>조회, 분석 --&gt; 그래프로 1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>에이전트</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>대시보드</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>예측</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1337,7 +1367,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A2:D135"/>
+  <dimension ref="A2:E135"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6" style="36" customWidth="1"/>
@@ -1431,22 +1461,22 @@
         <v>17</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B16" s="19"/>
       <c r="C16" s="20" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B17" s="19"/>
       <c r="C17" s="20" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B18" s="7" t="s">
         <v>19</v>
       </c>
@@ -1454,25 +1484,25 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B19" s="5"/>
       <c r="C19" s="11" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B20" s="5"/>
       <c r="C20" s="11" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="21" spans="2:3" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B21" s="3"/>
       <c r="C21" s="12" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="2:3" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B22" s="3" t="s">
         <v>24</v>
       </c>
@@ -1480,32 +1510,41 @@
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="2:3" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
-    <row r="24" spans="2:3" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="24" spans="2:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B24" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="25" spans="2:3" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="D24" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B25" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="26" spans="2:3" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="D25" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B26" s="21" t="s">
         <v>6</v>
       </c>
       <c r="C26" s="22" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="D26" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B27" s="40" t="s">
         <v>9</v>
       </c>
@@ -1513,13 +1552,13 @@
         <v>29</v>
       </c>
     </row>
-    <row r="28" spans="2:3" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B28" s="41"/>
       <c r="C28" s="6" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B29" s="17" t="s">
         <v>11</v>
       </c>
@@ -1527,7 +1566,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B30" s="19" t="s">
         <v>13</v>
       </c>
@@ -1535,13 +1574,13 @@
         <v>32</v>
       </c>
     </row>
-    <row r="31" spans="2:3" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B31" s="19"/>
       <c r="C31" s="23" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B32" s="17" t="s">
         <v>17</v>
       </c>
@@ -1670,7 +1709,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B49" s="19"/>
       <c r="C49" s="25" t="s">
         <v>53</v>
@@ -1679,13 +1718,13 @@
         <v>54</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B50" s="19"/>
       <c r="C50" s="25" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B51" s="7" t="s">
         <v>19</v>
       </c>
@@ -1693,25 +1732,25 @@
         <v>56</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B52" s="5"/>
       <c r="C52" s="6" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B53" s="5"/>
       <c r="C53" s="6" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B54" s="3"/>
       <c r="C54" s="4" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B55" s="3" t="s">
         <v>24</v>
       </c>
@@ -1719,8 +1758,8 @@
         <v>60</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
-    <row r="57" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="57" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A57" s="29"/>
       <c r="B57" s="1" t="s">
         <v>2</v>
@@ -1728,24 +1767,36 @@
       <c r="C57" s="2" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="58" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="D57" t="s">
+        <v>207</v>
+      </c>
+      <c r="E57" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B58" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="59" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="D58" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B59" s="21" t="s">
         <v>6</v>
       </c>
       <c r="C59" s="22" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="D59" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B60" s="5" t="s">
         <v>9</v>
       </c>
@@ -1753,25 +1804,25 @@
         <v>63</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B61" s="5"/>
       <c r="C61" s="6" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B62" s="5"/>
       <c r="C62" s="6" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B63" s="5"/>
       <c r="C63" s="6" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="64" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B64" s="5"/>
       <c r="C64" s="6" t="s">
         <v>67</v>
@@ -1834,13 +1885,13 @@
     <row r="72" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B72" s="19"/>
       <c r="C72" s="20" t="s">
-        <v>77</v>
+        <v>204</v>
       </c>
     </row>
     <row r="73" spans="2:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B73" s="19"/>
       <c r="C73" s="20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="74" spans="2:4" x14ac:dyDescent="0.4">
@@ -1848,37 +1899,37 @@
         <v>19</v>
       </c>
       <c r="C74" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="75" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B75" s="5"/>
       <c r="C75" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="76" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B76" s="5"/>
       <c r="C76" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="77" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B77" s="5"/>
       <c r="C77" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="78" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B78" s="5"/>
       <c r="C78" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="79" spans="2:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B79" s="3"/>
       <c r="C79" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="80" spans="2:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
@@ -1895,10 +1946,10 @@
         <v>2</v>
       </c>
       <c r="C82" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D82" t="s">
         <v>85</v>
-      </c>
-      <c r="D82" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="83" spans="2:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
@@ -1906,10 +1957,10 @@
         <v>4</v>
       </c>
       <c r="C83" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D83" t="s">
         <v>87</v>
-      </c>
-      <c r="D83" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="84" spans="2:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
@@ -1917,7 +1968,7 @@
         <v>6</v>
       </c>
       <c r="C84" s="22" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="85" spans="2:4" x14ac:dyDescent="0.4">
@@ -1925,25 +1976,25 @@
         <v>9</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="86" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B86" s="5"/>
       <c r="C86" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="87" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B87" s="5"/>
       <c r="C87" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="88" spans="2:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B88" s="5"/>
       <c r="C88" s="6" t="s">
-        <v>93</v>
+        <v>205</v>
       </c>
     </row>
     <row r="89" spans="2:4" x14ac:dyDescent="0.4">
@@ -1951,7 +2002,7 @@
         <v>11</v>
       </c>
       <c r="C89" s="33" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="90" spans="2:4" x14ac:dyDescent="0.4">
@@ -1959,31 +2010,31 @@
         <v>13</v>
       </c>
       <c r="C90" s="20" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="91" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B91" s="19"/>
       <c r="C91" s="31" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="92" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B92" s="19"/>
       <c r="C92" s="25" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="93" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B93" s="19"/>
       <c r="C93" s="31" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="94" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B94" s="19"/>
       <c r="C94" s="25" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="95" spans="2:4" x14ac:dyDescent="0.4">
@@ -1993,19 +2044,19 @@
     <row r="96" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B96" s="19"/>
       <c r="C96" s="32" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="97" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B97" s="19"/>
       <c r="C97" s="31" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="98" spans="2:3" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B98" s="19"/>
       <c r="C98" s="32" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="99" spans="2:3" x14ac:dyDescent="0.4">
@@ -2013,31 +2064,31 @@
         <v>17</v>
       </c>
       <c r="C99" s="18" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="100" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B100" s="19"/>
       <c r="C100" s="20" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="101" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B101" s="19"/>
       <c r="C101" s="20" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="102" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B102" s="19"/>
       <c r="C102" s="25" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="103" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B103" s="19"/>
       <c r="C103" s="30" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="104" spans="2:3" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
@@ -2049,25 +2100,25 @@
         <v>19</v>
       </c>
       <c r="C105" s="10" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="106" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B106" s="5"/>
       <c r="C106" s="6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="107" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B107" s="5"/>
       <c r="C107" s="6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="108" spans="2:3" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B108" s="3"/>
       <c r="C108" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="109" spans="2:3" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
@@ -2084,7 +2135,7 @@
         <v>2</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="112" spans="2:3" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
@@ -2092,7 +2143,7 @@
         <v>4</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="113" spans="2:3" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
@@ -2100,7 +2151,7 @@
         <v>6</v>
       </c>
       <c r="C113" s="22" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="114" spans="2:3" x14ac:dyDescent="0.4">
@@ -2108,25 +2159,25 @@
         <v>9</v>
       </c>
       <c r="C114" s="6" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="115" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B115" s="5"/>
       <c r="C115" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="116" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B116" s="5"/>
       <c r="C116" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="117" spans="2:3" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B117" s="5"/>
       <c r="C117" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="118" spans="2:3" x14ac:dyDescent="0.4">
@@ -2134,7 +2185,7 @@
         <v>11</v>
       </c>
       <c r="C118" s="18" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="119" spans="2:3" x14ac:dyDescent="0.4">
@@ -2142,37 +2193,37 @@
         <v>13</v>
       </c>
       <c r="C119" s="20" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="120" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B120" s="19"/>
       <c r="C120" s="20" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="121" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B121" s="19"/>
       <c r="C121" s="20" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="122" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B122" s="19"/>
       <c r="C122" s="25" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="123" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B123" s="19"/>
       <c r="C123" s="25" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="124" spans="2:3" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B124" s="19"/>
       <c r="C124" s="25" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="125" spans="2:3" x14ac:dyDescent="0.4">
@@ -2180,31 +2231,31 @@
         <v>17</v>
       </c>
       <c r="C125" s="18" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="126" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B126" s="19"/>
       <c r="C126" s="20" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="127" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B127" s="19"/>
       <c r="C127" s="25" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="128" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B128" s="19"/>
       <c r="C128" s="25" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="129" spans="2:3" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B129" s="19"/>
       <c r="C129" s="25" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="130" spans="2:3" x14ac:dyDescent="0.4">
@@ -2212,31 +2263,31 @@
         <v>19</v>
       </c>
       <c r="C130" s="10" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="131" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B131" s="5"/>
       <c r="C131" s="6" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="132" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B132" s="5"/>
       <c r="C132" s="6" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="133" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B133" s="5"/>
       <c r="C133" s="6" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="134" spans="2:3" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B134" s="3"/>
       <c r="C134" s="4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="135" spans="2:3" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
@@ -2244,7 +2295,7 @@
         <v>24</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -2292,10 +2343,10 @@
         <v>2</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D7" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="8" spans="2:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
@@ -2303,7 +2354,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="9" spans="2:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
@@ -2311,7 +2362,7 @@
         <v>6</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="10" spans="2:4" ht="52.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
@@ -2319,7 +2370,7 @@
         <v>9</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11" spans="2:4" x14ac:dyDescent="0.4">
@@ -2327,7 +2378,7 @@
         <v>11</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12" spans="2:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
@@ -2341,7 +2392,7 @@
         <v>17</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.4">
@@ -2349,13 +2400,13 @@
         <v>19</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="15" spans="2:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B15" s="3"/>
       <c r="C15" s="12" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="16" spans="2:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
@@ -2410,7 +2461,7 @@
         <v>2</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" spans="2:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
@@ -2418,7 +2469,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="9" spans="2:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
@@ -2426,7 +2477,7 @@
         <v>6</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10" spans="2:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
@@ -2434,7 +2485,7 @@
         <v>9</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11" spans="2:4" x14ac:dyDescent="0.4">
@@ -2442,7 +2493,7 @@
         <v>11</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="12" spans="2:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
@@ -2450,7 +2501,7 @@
         <v>13</v>
       </c>
       <c r="C12" s="22" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13" spans="2:4" x14ac:dyDescent="0.4">
@@ -2458,19 +2509,19 @@
         <v>17</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D13" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="14" spans="2:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B14" s="19"/>
       <c r="C14" s="25" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D14" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="15" spans="2:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
@@ -2478,7 +2529,7 @@
         <v>19</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="16" spans="2:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
@@ -2495,7 +2546,7 @@
         <v>2</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="19" spans="2:3" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
@@ -2503,7 +2554,7 @@
         <v>4</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
@@ -2511,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
@@ -2519,7 +2570,7 @@
         <v>9</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.4">
@@ -2527,7 +2578,7 @@
         <v>11</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="23" spans="2:3" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
@@ -2535,7 +2586,7 @@
         <v>13</v>
       </c>
       <c r="C23" s="25" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.4">
@@ -2543,19 +2594,19 @@
         <v>17</v>
       </c>
       <c r="C24" s="24" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B25" s="19"/>
       <c r="C25" s="25" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="26" spans="2:3" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B26" s="19"/>
       <c r="C26" s="25" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="27" spans="2:3" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
@@ -2563,7 +2614,7 @@
         <v>19</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="28" spans="2:3" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
@@ -2571,7 +2622,7 @@
         <v>24</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="29" spans="2:3" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
@@ -2580,7 +2631,7 @@
         <v>2</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="31" spans="2:3" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
@@ -2588,7 +2639,7 @@
         <v>4</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="32" spans="2:3" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
@@ -2596,7 +2647,7 @@
         <v>6</v>
       </c>
       <c r="C32" s="22" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="33" spans="2:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
@@ -2604,10 +2655,10 @@
         <v>9</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D33" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="34" spans="2:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
@@ -2615,7 +2666,7 @@
         <v>11</v>
       </c>
       <c r="C34" s="24" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.4">
@@ -2623,22 +2674,22 @@
         <v>17</v>
       </c>
       <c r="C35" s="24" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="36" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B36" s="19"/>
       <c r="C36" s="25" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="37" spans="2:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B37" s="19"/>
       <c r="C37" s="25" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D37" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="38" spans="2:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
@@ -2646,7 +2697,7 @@
         <v>19</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="39" spans="2:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
@@ -2659,7 +2710,7 @@
     </row>
     <row r="40" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B40" s="16" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -2708,7 +2759,7 @@
         <v>2</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
@@ -2716,7 +2767,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
@@ -2724,7 +2775,7 @@
         <v>6</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="10" spans="2:3" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
@@ -2732,7 +2783,7 @@
         <v>9</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.4">
@@ -2740,7 +2791,7 @@
         <v>11</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.4">
@@ -2748,7 +2799,7 @@
         <v>13</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="13" spans="2:3" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
@@ -2762,19 +2813,19 @@
         <v>17</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B15" s="19"/>
       <c r="C15" s="20" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="16" spans="2:3" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B16" s="19"/>
       <c r="C16" s="20" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.4">
@@ -2782,19 +2833,19 @@
         <v>19</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B18" s="5"/>
       <c r="C18" s="11" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="19" spans="2:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B19" s="3"/>
       <c r="C19" s="12" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="20" spans="2:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
@@ -2811,7 +2862,7 @@
         <v>2</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="23" spans="2:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
@@ -2819,7 +2870,7 @@
         <v>4</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="24" spans="2:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
@@ -2827,7 +2878,7 @@
         <v>6</v>
       </c>
       <c r="C24" s="22" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="25" spans="2:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
@@ -2835,7 +2886,7 @@
         <v>9</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="26" spans="2:4" x14ac:dyDescent="0.4">
@@ -2843,7 +2894,7 @@
         <v>11</v>
       </c>
       <c r="C26" s="18" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="27" spans="2:4" x14ac:dyDescent="0.4">
@@ -2851,13 +2902,13 @@
         <v>13</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="28" spans="2:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B28" s="19"/>
       <c r="C28" s="20" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="29" spans="2:4" x14ac:dyDescent="0.4">
@@ -2865,19 +2916,19 @@
         <v>17</v>
       </c>
       <c r="C29" s="18" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="30" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B30" s="19"/>
       <c r="C30" s="20" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="31" spans="2:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B31" s="19"/>
       <c r="C31" s="20" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="32" spans="2:4" x14ac:dyDescent="0.4">
@@ -2885,22 +2936,22 @@
         <v>19</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D32" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B33" s="5"/>
       <c r="C33" s="11" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="34" spans="2:3" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B34" s="3"/>
       <c r="C34" s="12" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="35" spans="2:3" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
